--- a/artfynd/A 3913-2022 artfynd.xlsx
+++ b/artfynd/A 3913-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3913-2022 artfynd.xlsx
+++ b/artfynd/A 3913-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55265234</v>
+        <v>7229155</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,21 +713,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sidsjöns utlopp, 1,85 km SO, Jmt</t>
+          <t>Sundsveområtet, Sidsjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508274.8422917173</v>
+        <v>508155</v>
       </c>
       <c r="R2" t="n">
-        <v>6954083.624295417</v>
+        <v>6954103</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,13 +773,13 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>luckig granskog med översilad rännilar på vitmossor</t>
+          <t>Granskogkärr på fuktig tuvig vitmossemark. Skogsfräken.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Bo Norell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -803,64 +791,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55265246</v>
+        <v>7229153</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sidsjöns utlopp, 1,9 km SO, Jmt</t>
+          <t>Sundsveområtet, Sidsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508053.2929653712</v>
+        <v>508195</v>
       </c>
       <c r="R3" t="n">
-        <v>6954128.493495735</v>
+        <v>6954129</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,27 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spindelblomster</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,13 +889,13 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>luckig granskog</t>
+          <t>Blåbärsgranskog på frisk mossig mark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Bo Norell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -936,47 +907,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7229155</v>
+        <v>7229163</v>
       </c>
       <c r="B4" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>620</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -986,17 +952,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundsveområtet, Sidsjö, Jmt</t>
+          <t>Sidsjöbergets norrsida, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508155.3454063633</v>
+        <v>508025</v>
       </c>
       <c r="R4" t="n">
-        <v>6954103.053549469</v>
+        <v>6954130</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,22 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1005,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskogkärr på fuktig tuvig vitmossemark. Skogsfräken.</t>
+          <t>Granskog på sluttande mossig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1064,6 +1020,237 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>55265234</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sidsjöns utlopp, 1,85 km SO, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508275</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6954084</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>luckig granskog med översilad rännilar på vitmossor</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>55265246</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sidsjöns utlopp, 1,9 km SO, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508053</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6954128</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spindelblomster</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>luckig granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3913-2022 artfynd.xlsx
+++ b/artfynd/A 3913-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229155</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229153</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229163</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55265234</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,8 +1276,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55265246</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>